--- a/语文群_20260816.xlsx
+++ b/语文群_20260816.xlsx
@@ -1041,7 +1041,7 @@
     <row r="1" spans="1:4">
       <c r="B1">
         <f>SUM(B3:B10000)</f>
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1394,10 +1394,10 @@
       </c>
       <c r="B25" s="2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2">
         <v>12</v>
